--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/85.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/85.xlsx
@@ -426,13 +426,13 @@
         <v>-13.38561025227457</v>
       </c>
       <c r="E2">
-        <v>-8.272038749246828</v>
+        <v>-9.989947063374633</v>
       </c>
       <c r="F2">
-        <v>5.113381119063251</v>
+        <v>3.952526266752052</v>
       </c>
       <c r="G2">
-        <v>-14.33165736036292</v>
+        <v>-13.09799580733566</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.25968093010681</v>
       </c>
       <c r="E3">
-        <v>-9.933730587043414</v>
+        <v>-8.813965762218748</v>
       </c>
       <c r="F3">
-        <v>5.260992012617701</v>
+        <v>3.759469348248153</v>
       </c>
       <c r="G3">
-        <v>-12.87216363282874</v>
+        <v>-13.09975039647148</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.85960040620665</v>
       </c>
       <c r="E4">
-        <v>-10.20451069033206</v>
+        <v>-9.751042888625976</v>
       </c>
       <c r="F4">
-        <v>5.028974344888075</v>
+        <v>4.280054070829999</v>
       </c>
       <c r="G4">
-        <v>-13.08881566455527</v>
+        <v>-11.6534491929113</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.338593428334597</v>
       </c>
       <c r="E5">
-        <v>-9.505726394682457</v>
+        <v>-9.981044083475552</v>
       </c>
       <c r="F5">
-        <v>5.188242897686075</v>
+        <v>4.419814534161615</v>
       </c>
       <c r="G5">
-        <v>-12.06212941864325</v>
+        <v>-12.35237156716223</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.697234434780614</v>
       </c>
       <c r="E6">
-        <v>-10.96750874741043</v>
+        <v>-13.4540213694381</v>
       </c>
       <c r="F6">
-        <v>5.214130154579848</v>
+        <v>4.102251407703613</v>
       </c>
       <c r="G6">
-        <v>-11.36194241599632</v>
+        <v>-9.922775438073266</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.003747343268347</v>
       </c>
       <c r="E7">
-        <v>-11.89332808743459</v>
+        <v>-12.25190624478395</v>
       </c>
       <c r="F7">
-        <v>5.384674693495775</v>
+        <v>4.415114095004591</v>
       </c>
       <c r="G7">
-        <v>-10.21960226166986</v>
+        <v>-10.69364258798364</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.274245124854761</v>
       </c>
       <c r="E8">
-        <v>-14.00553516188426</v>
+        <v>-15.24470678934318</v>
       </c>
       <c r="F8">
-        <v>5.205378595691129</v>
+        <v>4.386092684104163</v>
       </c>
       <c r="G8">
-        <v>-9.206320414646353</v>
+        <v>-9.304368841882948</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.553684620006744</v>
       </c>
       <c r="E9">
-        <v>-13.88229727023952</v>
+        <v>-14.6296585065694</v>
       </c>
       <c r="F9">
-        <v>5.166465357642866</v>
+        <v>4.653734232695683</v>
       </c>
       <c r="G9">
-        <v>-8.045550453302775</v>
+        <v>-7.216533570995102</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.8540346045411592</v>
       </c>
       <c r="E10">
-        <v>-15.76294535478097</v>
+        <v>-14.86836342846173</v>
       </c>
       <c r="F10">
-        <v>5.027322539618272</v>
+        <v>4.264066559613639</v>
       </c>
       <c r="G10">
-        <v>-7.147012114670408</v>
+        <v>-6.169275595102055</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.7953908402853621</v>
       </c>
       <c r="E11">
-        <v>-15.08978316506677</v>
+        <v>-16.19465836735421</v>
       </c>
       <c r="F11">
-        <v>5.423445398011649</v>
+        <v>4.630989048338142</v>
       </c>
       <c r="G11">
-        <v>-5.388609230395438</v>
+        <v>-6.169076962369699</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.378239526222784</v>
       </c>
       <c r="E12">
-        <v>-16.65043569080421</v>
+        <v>-17.31654251801447</v>
       </c>
       <c r="F12">
-        <v>5.246369655900448</v>
+        <v>4.527702915945012</v>
       </c>
       <c r="G12">
-        <v>-5.730426367870727</v>
+        <v>-5.10183984414715</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.877413732180573</v>
       </c>
       <c r="E13">
-        <v>-17.23962185852018</v>
+        <v>-17.85795328494951</v>
       </c>
       <c r="F13">
-        <v>5.653416917698526</v>
+        <v>4.843820118902219</v>
       </c>
       <c r="G13">
-        <v>-4.490964739058673</v>
+        <v>-4.119988316473483</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.265857161805618</v>
       </c>
       <c r="E14">
-        <v>-18.27484460209564</v>
+        <v>-18.80146990139565</v>
       </c>
       <c r="F14">
-        <v>5.238970581863515</v>
+        <v>4.524969439534964</v>
       </c>
       <c r="G14">
-        <v>-3.826144294407773</v>
+        <v>-4.664986875876003</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.534236825117245</v>
       </c>
       <c r="E15">
-        <v>-19.66507706550243</v>
+        <v>-19.51402528650258</v>
       </c>
       <c r="F15">
-        <v>5.774603678053868</v>
+        <v>5.099458760360624</v>
       </c>
       <c r="G15">
-        <v>-1.759453477879252</v>
+        <v>-2.577803782459394</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.661133751072331</v>
       </c>
       <c r="E16">
-        <v>-20.25274166595182</v>
+        <v>-20.81125647921384</v>
       </c>
       <c r="F16">
-        <v>5.835191515260835</v>
+        <v>5.204749864442699</v>
       </c>
       <c r="G16">
-        <v>-1.390208470611101</v>
+        <v>-1.738246123154681</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>8.645719804988131</v>
       </c>
       <c r="E17">
-        <v>-21.73168240669486</v>
+        <v>-23.18713395276011</v>
       </c>
       <c r="F17">
-        <v>5.304523337115385</v>
+        <v>5.102086128474338</v>
       </c>
       <c r="G17">
-        <v>-1.676405132481095</v>
+        <v>-1.481658980587929</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>9.475424969486211</v>
       </c>
       <c r="E18">
-        <v>-22.16247613904454</v>
+        <v>-22.48706357049233</v>
       </c>
       <c r="F18">
-        <v>5.4642448298052</v>
+        <v>5.219676292695716</v>
       </c>
       <c r="G18">
-        <v>-0.2053211850139329</v>
+        <v>-1.247047239310858</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>10.15270770328932</v>
       </c>
       <c r="E19">
-        <v>-24.33463115240775</v>
+        <v>-23.58780880448478</v>
       </c>
       <c r="F19">
-        <v>5.36364624635057</v>
+        <v>5.470869471649483</v>
       </c>
       <c r="G19">
-        <v>-0.3970150139198917</v>
+        <v>-0.9296586173698509</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>10.66626775925595</v>
       </c>
       <c r="E20">
-        <v>-24.6262512930797</v>
+        <v>-25.05604876114769</v>
       </c>
       <c r="F20">
-        <v>5.781776282144893</v>
+        <v>5.887653357415682</v>
       </c>
       <c r="G20">
-        <v>-0.0599220249291424</v>
+        <v>-1.57617836627966</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>11.01802724267215</v>
       </c>
       <c r="E21">
-        <v>-25.79072121330808</v>
+        <v>-25.76876264284489</v>
       </c>
       <c r="F21">
-        <v>5.881190253574774</v>
+        <v>5.208181755161457</v>
       </c>
       <c r="G21">
-        <v>0.4816137038392991</v>
+        <v>0.3239158670761161</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>11.20088997893222</v>
       </c>
       <c r="E22">
-        <v>-25.18379701290407</v>
+        <v>-26.38670462050956</v>
       </c>
       <c r="F22">
-        <v>5.865592334013611</v>
+        <v>5.142183978547349</v>
       </c>
       <c r="G22">
-        <v>0.2867516828522578</v>
+        <v>1.021590165658744</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>11.22060298294931</v>
       </c>
       <c r="E23">
-        <v>-25.32201962504019</v>
+        <v>-26.48636274799636</v>
       </c>
       <c r="F23">
-        <v>5.468737803487302</v>
+        <v>5.158168322351879</v>
       </c>
       <c r="G23">
-        <v>0.5241376612912375</v>
+        <v>0.4498821248453848</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>11.08211579378677</v>
       </c>
       <c r="E24">
-        <v>-25.85705430057244</v>
+        <v>-26.45950889713088</v>
       </c>
       <c r="F24">
-        <v>5.600508470475525</v>
+        <v>5.264256030509421</v>
       </c>
       <c r="G24">
-        <v>1.728259216471572</v>
+        <v>0.4319488996591528</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>10.80272284784175</v>
       </c>
       <c r="E25">
-        <v>-26.67208452399894</v>
+        <v>-27.07734671989338</v>
       </c>
       <c r="F25">
-        <v>5.139437832489977</v>
+        <v>4.988323781450576</v>
       </c>
       <c r="G25">
-        <v>1.377665822771674</v>
+        <v>1.188974658669834</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>10.40272715099244</v>
       </c>
       <c r="E26">
-        <v>-27.10809958687947</v>
+        <v>-29.47088750630657</v>
       </c>
       <c r="F26">
-        <v>5.259145411520298</v>
+        <v>4.967521804251279</v>
       </c>
       <c r="G26">
-        <v>1.322952436644139</v>
+        <v>1.333592530007357</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>9.90795115870551</v>
       </c>
       <c r="E27">
-        <v>-26.72103732802186</v>
+        <v>-25.71593799354541</v>
       </c>
       <c r="F27">
-        <v>5.186394712882756</v>
+        <v>5.262284316644699</v>
       </c>
       <c r="G27">
-        <v>1.760222533653235</v>
+        <v>1.732556304581546</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>9.35037024953953</v>
       </c>
       <c r="E28">
-        <v>-26.99790822885082</v>
+        <v>-26.3210734467164</v>
       </c>
       <c r="F28">
-        <v>5.167748159434372</v>
+        <v>4.48652181102584</v>
       </c>
       <c r="G28">
-        <v>1.625728310574803</v>
+        <v>0.834497995052372</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.754916104226929</v>
       </c>
       <c r="E29">
-        <v>-26.11493730988724</v>
+        <v>-27.7385944944934</v>
       </c>
       <c r="F29">
-        <v>5.014568955881238</v>
+        <v>4.782754002508789</v>
       </c>
       <c r="G29">
-        <v>1.924379244763536</v>
+        <v>1.926560894273916</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.157438759608299</v>
       </c>
       <c r="E30">
-        <v>-26.49073272541377</v>
+        <v>-27.78683179962311</v>
       </c>
       <c r="F30">
-        <v>5.345468469853157</v>
+        <v>3.809812191888142</v>
       </c>
       <c r="G30">
-        <v>1.912348722273824</v>
+        <v>1.829330171785521</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.571940228840968</v>
       </c>
       <c r="E31">
-        <v>-26.48544346777281</v>
+        <v>-26.63147769757216</v>
       </c>
       <c r="F31">
-        <v>4.909345951153526</v>
+        <v>4.511824680436816</v>
       </c>
       <c r="G31">
-        <v>1.21216171962689</v>
+        <v>1.539233687270265</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.027144020353735</v>
       </c>
       <c r="E32">
-        <v>-26.24523509250994</v>
+        <v>-25.68635347285331</v>
       </c>
       <c r="F32">
-        <v>5.032886098499211</v>
+        <v>4.497786711202362</v>
       </c>
       <c r="G32">
-        <v>0.6835834660991557</v>
+        <v>2.892492008449227</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.525051650487199</v>
       </c>
       <c r="E33">
-        <v>-25.53526546606139</v>
+        <v>-26.16527582695651</v>
       </c>
       <c r="F33">
-        <v>4.876851473180539</v>
+        <v>4.816466350330749</v>
       </c>
       <c r="G33">
-        <v>0.7346585626790315</v>
+        <v>1.878918833418264</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.077171704197799</v>
       </c>
       <c r="E34">
-        <v>-25.38428614264566</v>
+        <v>-25.83020497818096</v>
       </c>
       <c r="F34">
-        <v>5.428635202296544</v>
+        <v>4.480156896951689</v>
       </c>
       <c r="G34">
-        <v>1.338379578857143</v>
+        <v>1.556475008438789</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.67638750622926</v>
       </c>
       <c r="E35">
-        <v>-23.96998483988811</v>
+        <v>-24.77990241615995</v>
       </c>
       <c r="F35">
-        <v>5.373553910557559</v>
+        <v>4.659319963459438</v>
       </c>
       <c r="G35">
-        <v>0.8319290117138975</v>
+        <v>0.1016756344793021</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.318205687699811</v>
       </c>
       <c r="E36">
-        <v>-23.26828873545157</v>
+        <v>-26.00041220223326</v>
       </c>
       <c r="F36">
-        <v>5.903556932218525</v>
+        <v>4.544480696413178</v>
       </c>
       <c r="G36">
-        <v>0.4456479371006569</v>
+        <v>0.1570213348048378</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.992954927275661</v>
       </c>
       <c r="E37">
-        <v>-23.4396960051159</v>
+        <v>-23.65750201946282</v>
       </c>
       <c r="F37">
-        <v>5.368410033744212</v>
+        <v>4.502917918368385</v>
       </c>
       <c r="G37">
-        <v>0.2980373325956333</v>
+        <v>-0.8868201580916817</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.687373258193222</v>
       </c>
       <c r="E38">
-        <v>-23.22873704346858</v>
+        <v>-23.36550148697423</v>
       </c>
       <c r="F38">
-        <v>6.002926559882773</v>
+        <v>4.843341839715756</v>
       </c>
       <c r="G38">
-        <v>0.240145822750398</v>
+        <v>-0.00657258356378722</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.397350432336175</v>
       </c>
       <c r="E39">
-        <v>-22.33844358203459</v>
+        <v>-23.60484945217564</v>
       </c>
       <c r="F39">
-        <v>5.536043721187562</v>
+        <v>5.148051608964052</v>
       </c>
       <c r="G39">
-        <v>-0.05097693088203165</v>
+        <v>0.2733472839637487</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.109333951874774</v>
       </c>
       <c r="E40">
-        <v>-22.2233252442856</v>
+        <v>-21.14721038042088</v>
       </c>
       <c r="F40">
-        <v>5.859103890878055</v>
+        <v>5.497095641609159</v>
       </c>
       <c r="G40">
-        <v>-0.05025854250000981</v>
+        <v>0.453791879127264</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.826441889373782</v>
       </c>
       <c r="E41">
-        <v>-22.03828273938418</v>
+        <v>-22.00304215465649</v>
       </c>
       <c r="F41">
-        <v>5.994635859415448</v>
+        <v>5.304998448890017</v>
       </c>
       <c r="G41">
-        <v>0.1683698849134594</v>
+        <v>-0.8401414659879579</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.540587643806749</v>
       </c>
       <c r="E42">
-        <v>-19.9551167687457</v>
+        <v>-20.51909292166097</v>
       </c>
       <c r="F42">
-        <v>6.085272932661963</v>
+        <v>5.611595995589516</v>
       </c>
       <c r="G42">
-        <v>-0.4225128356633585</v>
+        <v>-0.9205744804100907</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.257041299001227</v>
       </c>
       <c r="E43">
-        <v>-20.36292849550645</v>
+        <v>-18.92969364292283</v>
       </c>
       <c r="F43">
-        <v>6.185445499225339</v>
+        <v>5.541928772369335</v>
       </c>
       <c r="G43">
-        <v>-1.691574052142036</v>
+        <v>-0.7329460014263569</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.972106457631169</v>
       </c>
       <c r="E44">
-        <v>-18.37451178653046</v>
+        <v>-18.92689051751208</v>
       </c>
       <c r="F44">
-        <v>6.350987111154393</v>
+        <v>5.805802684588025</v>
       </c>
       <c r="G44">
-        <v>-1.426538397359063</v>
+        <v>-1.715469569844496</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.687177638681889</v>
       </c>
       <c r="E45">
-        <v>-17.92108021261643</v>
+        <v>-18.52566772043249</v>
       </c>
       <c r="F45">
-        <v>6.1914319075857</v>
+        <v>5.77147744257679</v>
       </c>
       <c r="G45">
-        <v>-2.195151065757194</v>
+        <v>-0.7887684203095476</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.398127657676695</v>
       </c>
       <c r="E46">
-        <v>-17.51902870479344</v>
+        <v>-17.87533809666496</v>
       </c>
       <c r="F46">
-        <v>6.707670941135581</v>
+        <v>5.566580738649066</v>
       </c>
       <c r="G46">
-        <v>-1.351339355434518</v>
+        <v>-1.795915826448785</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.102044254927305</v>
       </c>
       <c r="E47">
-        <v>-17.58712336844678</v>
+        <v>-16.28293191118573</v>
       </c>
       <c r="F47">
-        <v>6.424830566873588</v>
+        <v>6.12337531328152</v>
       </c>
       <c r="G47">
-        <v>-1.866569489347911</v>
+        <v>-1.786345039294752</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.794625971006167</v>
       </c>
       <c r="E48">
-        <v>-16.92846588097914</v>
+        <v>-16.08735617574246</v>
       </c>
       <c r="F48">
-        <v>6.803325194722208</v>
+        <v>6.243017960369309</v>
       </c>
       <c r="G48">
-        <v>-2.703376085309489</v>
+        <v>-3.054714351755722</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.469850286558793</v>
       </c>
       <c r="E49">
-        <v>-14.89896685580556</v>
+        <v>-16.0720861613886</v>
       </c>
       <c r="F49">
-        <v>7.012421886737679</v>
+        <v>6.114354524387177</v>
       </c>
       <c r="G49">
-        <v>-3.188867588643609</v>
+        <v>-2.492123553357516</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.125483496902452</v>
       </c>
       <c r="E50">
-        <v>-15.32066741234784</v>
+        <v>-14.91424592710744</v>
       </c>
       <c r="F50">
-        <v>6.937104000811209</v>
+        <v>5.861340083630656</v>
       </c>
       <c r="G50">
-        <v>-3.242336209648377</v>
+        <v>-2.687879421640161</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.7564243303103312</v>
       </c>
       <c r="E51">
-        <v>-13.742657245739</v>
+        <v>-15.51801830960211</v>
       </c>
       <c r="F51">
-        <v>7.335116220361705</v>
+        <v>6.377153100289283</v>
       </c>
       <c r="G51">
-        <v>-3.648166055671014</v>
+        <v>-3.738517464528804</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.364635284198824</v>
       </c>
       <c r="E52">
-        <v>-13.50715848344411</v>
+        <v>-13.27604328398864</v>
       </c>
       <c r="F52">
-        <v>7.334797895472701</v>
+        <v>6.461350825283622</v>
       </c>
       <c r="G52">
-        <v>-3.399381868940324</v>
+        <v>-3.356804942759757</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.05258873610562971</v>
       </c>
       <c r="E53">
-        <v>-13.52888610173291</v>
+        <v>-13.74582717754437</v>
       </c>
       <c r="F53">
-        <v>7.033584948885696</v>
+        <v>6.660443247031261</v>
       </c>
       <c r="G53">
-        <v>-3.871525252660102</v>
+        <v>-3.146956082116435</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.4908127573281544</v>
       </c>
       <c r="E54">
-        <v>-12.48284030527911</v>
+        <v>-12.13707320089745</v>
       </c>
       <c r="F54">
-        <v>7.315595461247998</v>
+        <v>6.472609390636481</v>
       </c>
       <c r="G54">
-        <v>-4.376158330302288</v>
+        <v>-4.363495493614575</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.9514998436631968</v>
       </c>
       <c r="E55">
-        <v>-13.44375079038871</v>
+        <v>-12.41284821101656</v>
       </c>
       <c r="F55">
-        <v>7.371503447474842</v>
+        <v>6.295281839284726</v>
       </c>
       <c r="G55">
-        <v>-4.146019136048773</v>
+        <v>-3.848569929890796</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.427080868266347</v>
       </c>
       <c r="E56">
-        <v>-11.87020569915143</v>
+        <v>-11.90964870775823</v>
       </c>
       <c r="F56">
-        <v>7.549752715669382</v>
+        <v>7.031047852009162</v>
       </c>
       <c r="G56">
-        <v>-5.266609006182216</v>
+        <v>-4.716042109182642</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.916014657735163</v>
       </c>
       <c r="E57">
-        <v>-10.89191493080039</v>
+        <v>-11.03243800773241</v>
       </c>
       <c r="F57">
-        <v>7.92757426850394</v>
+        <v>6.805973151012823</v>
       </c>
       <c r="G57">
-        <v>-5.231629782014276</v>
+        <v>-4.410693941367965</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.408926987578025</v>
       </c>
       <c r="E58">
-        <v>-10.63491044544308</v>
+        <v>-11.31755978820335</v>
       </c>
       <c r="F58">
-        <v>7.676099189897226</v>
+        <v>6.498054793579846</v>
       </c>
       <c r="G58">
-        <v>-5.178899412664765</v>
+        <v>-4.624899479940968</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.900599767868422</v>
       </c>
       <c r="E59">
-        <v>-10.31049509600758</v>
+        <v>-9.296157674555488</v>
       </c>
       <c r="F59">
-        <v>7.789950224452252</v>
+        <v>6.449737509805704</v>
       </c>
       <c r="G59">
-        <v>-6.587771588357944</v>
+        <v>-6.070740517671187</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.382375703569763</v>
       </c>
       <c r="E60">
-        <v>-10.64598256439183</v>
+        <v>-11.54998824512104</v>
       </c>
       <c r="F60">
-        <v>7.907686089617852</v>
+        <v>6.806707990557586</v>
       </c>
       <c r="G60">
-        <v>-6.684287233009855</v>
+        <v>-5.923176260803714</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.845402177628122</v>
       </c>
       <c r="E61">
-        <v>-10.12197019459425</v>
+        <v>-9.281512589614682</v>
       </c>
       <c r="F61">
-        <v>7.441477909642618</v>
+        <v>6.481772713063213</v>
       </c>
       <c r="G61">
-        <v>-6.518223647668934</v>
+        <v>-6.091335421470993</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.283635343673696</v>
       </c>
       <c r="E62">
-        <v>-9.884587587112174</v>
+        <v>-10.4971904939218</v>
       </c>
       <c r="F62">
-        <v>8.054060108852342</v>
+        <v>7.059736684667347</v>
       </c>
       <c r="G62">
-        <v>-6.928304234163996</v>
+        <v>-5.657687061281861</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.687524576743123</v>
       </c>
       <c r="E63">
-        <v>-9.107832025998501</v>
+        <v>-8.202504030859052</v>
       </c>
       <c r="F63">
-        <v>7.8539826220253</v>
+        <v>6.85358726936051</v>
       </c>
       <c r="G63">
-        <v>-7.479993406101382</v>
+        <v>-6.067989454328053</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.055175544361938</v>
       </c>
       <c r="E64">
-        <v>-7.844591559188816</v>
+        <v>-7.848096598070753</v>
       </c>
       <c r="F64">
-        <v>7.946786204964136</v>
+        <v>7.238988438706361</v>
       </c>
       <c r="G64">
-        <v>-7.377280420199954</v>
+        <v>-6.886750266555064</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.378301683929443</v>
       </c>
       <c r="E65">
-        <v>-8.1145655941041</v>
+        <v>-8.164012001793854</v>
       </c>
       <c r="F65">
-        <v>7.672241282287215</v>
+        <v>6.709946726536067</v>
       </c>
       <c r="G65">
-        <v>-8.098287443743365</v>
+        <v>-6.779107878345661</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.659678632141168</v>
       </c>
       <c r="E66">
-        <v>-8.503027151430079</v>
+        <v>-6.669828417540995</v>
       </c>
       <c r="F66">
-        <v>7.641515803821775</v>
+        <v>6.705947869099583</v>
       </c>
       <c r="G66">
-        <v>-7.360075515032362</v>
+        <v>-6.919299550297178</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.892358969561446</v>
       </c>
       <c r="E67">
-        <v>-7.121113494775384</v>
+        <v>-7.98704829452211</v>
       </c>
       <c r="F67">
-        <v>7.453240093476587</v>
+        <v>6.800533121193288</v>
       </c>
       <c r="G67">
-        <v>-8.950716504104763</v>
+        <v>-6.916717324776546</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.080040402748322</v>
       </c>
       <c r="E68">
-        <v>-6.779612212908948</v>
+        <v>-7.361004876857714</v>
       </c>
       <c r="F68">
-        <v>7.773238959632535</v>
+        <v>6.482268413014746</v>
       </c>
       <c r="G68">
-        <v>-8.593670857148828</v>
+        <v>-7.627872164795087</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.218255703798748</v>
       </c>
       <c r="E69">
-        <v>-6.557762271273177</v>
+        <v>-7.098167716978519</v>
       </c>
       <c r="F69">
-        <v>7.456364745247749</v>
+        <v>6.505368347497346</v>
       </c>
       <c r="G69">
-        <v>-7.946525415132095</v>
+        <v>-7.723815085068705</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.309820895064864</v>
       </c>
       <c r="E70">
-        <v>-7.252815104340462</v>
+        <v>-5.657940900527054</v>
       </c>
       <c r="F70">
-        <v>7.358231991903459</v>
+        <v>6.728791243223881</v>
       </c>
       <c r="G70">
-        <v>-9.022121660841304</v>
+        <v>-7.227024689809053</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.354799575225683</v>
       </c>
       <c r="E71">
-        <v>-7.429615786547928</v>
+        <v>-6.285514942406043</v>
       </c>
       <c r="F71">
-        <v>7.365977897535873</v>
+        <v>6.448183894302658</v>
       </c>
       <c r="G71">
-        <v>-9.039760247474542</v>
+        <v>-8.203777977352242</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.355694818472688</v>
       </c>
       <c r="E72">
-        <v>-7.734866633982963</v>
+        <v>-6.860590385114109</v>
       </c>
       <c r="F72">
-        <v>7.011804241430657</v>
+        <v>6.270536434355985</v>
       </c>
       <c r="G72">
-        <v>-9.291368329550229</v>
+        <v>-8.324255350617399</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.317956796555781</v>
       </c>
       <c r="E73">
-        <v>-6.84066509948036</v>
+        <v>-5.627151805748904</v>
       </c>
       <c r="F73">
-        <v>7.186677048613481</v>
+        <v>5.877383024554057</v>
       </c>
       <c r="G73">
-        <v>-9.3787170736039</v>
+        <v>-7.313509381476973</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.243737549832407</v>
       </c>
       <c r="E74">
-        <v>-7.460219213891764</v>
+        <v>-6.201593262095896</v>
       </c>
       <c r="F74">
-        <v>7.119646695742506</v>
+        <v>6.073327038941803</v>
       </c>
       <c r="G74">
-        <v>-8.933389108752218</v>
+        <v>-7.186328153494792</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.142517159148749</v>
       </c>
       <c r="E75">
-        <v>-7.559750544106351</v>
+        <v>-7.271757711114547</v>
       </c>
       <c r="F75">
-        <v>6.806302561843234</v>
+        <v>6.176928328812105</v>
       </c>
       <c r="G75">
-        <v>-8.196127306610986</v>
+        <v>-8.284101743771579</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.013294635892524</v>
       </c>
       <c r="E76">
-        <v>-7.798351311096495</v>
+        <v>-6.841684006132085</v>
       </c>
       <c r="F76">
-        <v>6.922117391733406</v>
+        <v>5.930193282010301</v>
       </c>
       <c r="G76">
-        <v>-8.537219434613174</v>
+        <v>-7.199924564024578</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.866667911910417</v>
       </c>
       <c r="E77">
-        <v>-8.295016226361749</v>
+        <v>-8.508370750759131</v>
       </c>
       <c r="F77">
-        <v>7.006720545442096</v>
+        <v>5.791018789867397</v>
       </c>
       <c r="G77">
-        <v>-8.883674646388982</v>
+        <v>-6.907219369624378</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.700024803023248</v>
       </c>
       <c r="E78">
-        <v>-8.621396933516575</v>
+        <v>-9.05915998736406</v>
       </c>
       <c r="F78">
-        <v>6.981227631321268</v>
+        <v>6.079653944073983</v>
       </c>
       <c r="G78">
-        <v>-8.658305948257558</v>
+        <v>-8.111748121906041</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.520884584919383</v>
       </c>
       <c r="E79">
-        <v>-8.163577268289117</v>
+        <v>-8.362531245342106</v>
       </c>
       <c r="F79">
-        <v>6.660805915685897</v>
+        <v>5.689737629163214</v>
       </c>
       <c r="G79">
-        <v>-8.302541482425319</v>
+        <v>-7.186374501132342</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.326247442958651</v>
       </c>
       <c r="E80">
-        <v>-9.70665478640279</v>
+        <v>-8.282051205277789</v>
       </c>
       <c r="F80">
-        <v>6.756403155859569</v>
+        <v>5.879669895895952</v>
       </c>
       <c r="G80">
-        <v>-8.449880622196122</v>
+        <v>-6.643838987611041</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.118126621536744</v>
       </c>
       <c r="E81">
-        <v>-9.944281931481285</v>
+        <v>-8.731121858722426</v>
       </c>
       <c r="F81">
-        <v>7.070588237599939</v>
+        <v>5.567648156436072</v>
       </c>
       <c r="G81">
-        <v>-8.856352714053378</v>
+        <v>-7.485164478233724</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.893893256329702</v>
       </c>
       <c r="E82">
-        <v>-10.7224186771673</v>
+        <v>-9.63234252793692</v>
       </c>
       <c r="F82">
-        <v>6.592698642792423</v>
+        <v>5.803829387017387</v>
       </c>
       <c r="G82">
-        <v>-7.505471364571613</v>
+        <v>-6.324275337250732</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.650896939947287</v>
       </c>
       <c r="E83">
-        <v>-11.82082269009778</v>
+        <v>-10.51671727384288</v>
       </c>
       <c r="F83">
-        <v>6.612982748157371</v>
+        <v>5.832394690614168</v>
       </c>
       <c r="G83">
-        <v>-8.73269721707052</v>
+        <v>-6.034019946549591</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.387974874123943</v>
       </c>
       <c r="E84">
-        <v>-13.54681433032928</v>
+        <v>-11.33603143368064</v>
       </c>
       <c r="F84">
-        <v>6.780633856365792</v>
+        <v>5.665963035960638</v>
       </c>
       <c r="G84">
-        <v>-7.854038704401476</v>
+        <v>-5.889617260672122</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.099027066241878</v>
       </c>
       <c r="E85">
-        <v>-14.25005917287644</v>
+        <v>-13.84385958286241</v>
       </c>
       <c r="F85">
-        <v>6.510661092666744</v>
+        <v>5.960543422173783</v>
       </c>
       <c r="G85">
-        <v>-7.31724698739081</v>
+        <v>-5.192078694456604</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.785032752648821</v>
       </c>
       <c r="E86">
-        <v>-15.63036974973242</v>
+        <v>-13.53002727718284</v>
       </c>
       <c r="F86">
-        <v>6.839283237532261</v>
+        <v>5.668496965425341</v>
       </c>
       <c r="G86">
-        <v>-7.714485967739039</v>
+        <v>-4.758758078275859</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.439435677517003</v>
       </c>
       <c r="E87">
-        <v>-15.92787237814033</v>
+        <v>-15.15759253485762</v>
       </c>
       <c r="F87">
-        <v>6.568260476811277</v>
+        <v>5.631140510291955</v>
       </c>
       <c r="G87">
-        <v>-6.780862467481475</v>
+        <v>-5.469826844110377</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.067263393237022</v>
       </c>
       <c r="E88">
-        <v>-17.30126797518659</v>
+        <v>-15.78018072685417</v>
       </c>
       <c r="F88">
-        <v>6.324102119533893</v>
+        <v>5.008243634454973</v>
       </c>
       <c r="G88">
-        <v>-6.329522551930477</v>
+        <v>-4.098684955928273</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.666800932225535</v>
       </c>
       <c r="E89">
-        <v>-17.96652344928341</v>
+        <v>-18.89789469844097</v>
       </c>
       <c r="F89">
-        <v>6.56637745047782</v>
+        <v>5.097224151313938</v>
       </c>
       <c r="G89">
-        <v>-6.247149557822331</v>
+        <v>-4.021396959768448</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.245982774136561</v>
       </c>
       <c r="E90">
-        <v>-20.02235555081159</v>
+        <v>-19.64627031294857</v>
       </c>
       <c r="F90">
-        <v>5.977466903586168</v>
+        <v>5.518453499584776</v>
       </c>
       <c r="G90">
-        <v>-5.683108740477924</v>
+        <v>-4.407572096924432</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.808663241351316</v>
       </c>
       <c r="E91">
-        <v>-21.65731580654089</v>
+        <v>-22.3441766301283</v>
       </c>
       <c r="F91">
-        <v>5.958790259725391</v>
+        <v>5.419359436749815</v>
       </c>
       <c r="G91">
-        <v>-5.292265734111568</v>
+        <v>-4.026263461711177</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.364534733080836</v>
       </c>
       <c r="E92">
-        <v>-24.00268042222349</v>
+        <v>-24.28757577899405</v>
       </c>
       <c r="F92">
-        <v>5.953073081370655</v>
+        <v>4.796101475964113</v>
       </c>
       <c r="G92">
-        <v>-5.684724286701089</v>
+        <v>-2.70691174794543</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.9208948829969619</v>
       </c>
       <c r="E93">
-        <v>-25.73003060465728</v>
+        <v>-24.71946540205358</v>
       </c>
       <c r="F93">
-        <v>5.693761825894346</v>
+        <v>4.990145043253331</v>
       </c>
       <c r="G93">
-        <v>-4.61589479607415</v>
+        <v>-2.551355834146156</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4862254571454967</v>
       </c>
       <c r="E94">
-        <v>-27.32900307744763</v>
+        <v>-26.57025272898846</v>
       </c>
       <c r="F94">
-        <v>5.247595444278998</v>
+        <v>4.52587373561268</v>
       </c>
       <c r="G94">
-        <v>-3.314797430411945</v>
+        <v>-2.129774412447667</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.06798913644686982</v>
       </c>
       <c r="E95">
-        <v>-29.55540920942273</v>
+        <v>-29.28831075550232</v>
       </c>
       <c r="F95">
-        <v>5.004648622026926</v>
+        <v>3.981832744717259</v>
       </c>
       <c r="G95">
-        <v>-3.858392318505814</v>
+        <v>-2.022453147155573</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3307288682525317</v>
       </c>
       <c r="E96">
-        <v>-32.11521744750156</v>
+        <v>-31.46898156423696</v>
       </c>
       <c r="F96">
-        <v>4.563984034761814</v>
+        <v>3.099961942763957</v>
       </c>
       <c r="G96">
-        <v>-3.704547956750342</v>
+        <v>-2.798984640483641</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.7032478420982358</v>
       </c>
       <c r="E97">
-        <v>-34.13094764745481</v>
+        <v>-33.94803352533699</v>
       </c>
       <c r="F97">
-        <v>4.240779747833017</v>
+        <v>3.311762020777083</v>
       </c>
       <c r="G97">
-        <v>-3.188599434454928</v>
+        <v>-1.377145057913137</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.049490091494915</v>
       </c>
       <c r="E98">
-        <v>-36.08094704718673</v>
+        <v>-35.36855015867007</v>
       </c>
       <c r="F98">
-        <v>3.827101509366994</v>
+        <v>2.653667280969459</v>
       </c>
       <c r="G98">
-        <v>-3.115353614398552</v>
+        <v>-2.004576201243509</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.363865000096948</v>
       </c>
       <c r="E99">
-        <v>-38.26826339152762</v>
+        <v>-37.81305439156559</v>
       </c>
       <c r="F99">
-        <v>3.605552137738424</v>
+        <v>2.632667340530732</v>
       </c>
       <c r="G99">
-        <v>-2.549842914834709</v>
+        <v>-1.318743724054854</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.647247660930795</v>
       </c>
       <c r="E100">
-        <v>-40.51906667721904</v>
+        <v>-39.5420099180351</v>
       </c>
       <c r="F100">
-        <v>3.142352999002525</v>
+        <v>2.154115756650563</v>
       </c>
       <c r="G100">
-        <v>-2.821353996692496</v>
+        <v>-2.789433716602844</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.893696761421023</v>
       </c>
       <c r="E101">
-        <v>-42.7891906972642</v>
+        <v>-43.07226334324667</v>
       </c>
       <c r="F101">
-        <v>2.756359523644299</v>
+        <v>2.110077646259938</v>
       </c>
       <c r="G101">
-        <v>-2.38213398836077</v>
+        <v>-1.126248743128392</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.104546222821722</v>
       </c>
       <c r="E102">
-        <v>-44.71346610039554</v>
+        <v>-46.13405292507574</v>
       </c>
       <c r="F102">
-        <v>2.364506336398947</v>
+        <v>1.219067277468636</v>
       </c>
       <c r="G102">
-        <v>-2.51813119911403</v>
+        <v>-1.525262175885669</v>
       </c>
     </row>
   </sheetData>
